--- a/06-人事行政/人事刘萍萍/招聘进度表20260827.xlsx
+++ b/06-人事行政/人事刘萍萍/招聘进度表20260827.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22350" windowHeight="10680"/>
+    <workbookView windowWidth="27950" windowHeight="14080"/>
   </bookViews>
   <sheets>
     <sheet name="招聘需求进度表" sheetId="1" r:id="rId1"/>
@@ -1768,7 +1768,7 @@
     <numFmt numFmtId="185" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="186" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1983,27 +1983,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2151,12 +2137,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2567,58 +2547,112 @@
     <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="30" fillId="0" borderId="0">
@@ -2633,64 +2667,10 @@
     <xf numFmtId="176" fontId="30" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="30" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3831,12 +3811,12 @@
       <c r="I10" s="47"/>
       <c r="J10" s="48"/>
       <c r="K10" s="47">
-        <f ca="1">COUNTIFS(S18:S4992,TODAY())</f>
+        <f>COUNTIFS(S18:S4992,TODAY())</f>
         <v>0</v>
       </c>
       <c r="L10" s="47"/>
       <c r="M10" s="47">
-        <f ca="1">COUNTIFS(AD18:AD4992,TODAY())</f>
+        <f>COUNTIFS(AD18:AD4992,TODAY())</f>
         <v>0</v>
       </c>
       <c r="N10" s="47"/>
@@ -3915,7 +3895,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="38"/>
       <c r="E12" s="47">
-        <f ca="1">COUNTIFS(G18:G4992,TODAY())</f>
+        <f>COUNTIFS(G18:G4992,TODAY())</f>
         <v>0</v>
       </c>
       <c r="F12" s="47"/>
@@ -3924,12 +3904,12 @@
       <c r="I12" s="47"/>
       <c r="J12" s="48"/>
       <c r="K12" s="47">
-        <f ca="1">COUNTIFS(S18:S4992,"&gt;"&amp;TODAY(),S18:S4992,"&lt;="&amp;TODAY()+7)</f>
+        <f>COUNTIFS(S18:S4992,"&gt;"&amp;TODAY(),S18:S4992,"&lt;="&amp;TODAY()+7)</f>
         <v>0</v>
       </c>
       <c r="L12" s="47"/>
       <c r="M12" s="47">
-        <f ca="1">COUNTIFS(AD18:AD4992,"&gt;"&amp;TODAY(),AD18:AD4992,"&lt;="&amp;TODAY()+7)</f>
+        <f>COUNTIFS(AD18:AD4992,"&gt;"&amp;TODAY(),AD18:AD4992,"&lt;="&amp;TODAY()+7)</f>
         <v>0</v>
       </c>
       <c r="N12" s="47"/>
